--- a/Result/profitability/2316.xlsx
+++ b/Result/profitability/2316.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>2.40125</v>
+        <v>2.64875</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8412499999999998</v>
+        <v>-0.3349999999999997</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>2.17375</v>
+        <v>2.39125</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5412499999999998</v>
+        <v>-0.4024999999999997</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.63</v>
       </c>
       <c r="M4" t="n">
-        <v>2.0925</v>
+        <v>2.287500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5337500000000002</v>
+        <v>0.2987500000000002</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.91</v>
       </c>
       <c r="M5" t="n">
-        <v>1.79625</v>
+        <v>1.655</v>
       </c>
       <c r="N5" t="n">
-        <v>1.335</v>
+        <v>1.92875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2925</v>
+        <v>1.02125</v>
       </c>
       <c r="N6" t="n">
-        <v>2.85375</v>
+        <v>2.45125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6612500000000001</v>
+        <v>0.7175000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>3.755</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3712500000000001</v>
+        <v>0.3075000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>4.0875</v>
+        <v>2.87125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1172</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-185</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>899</v>
+      </c>
+      <c r="J75" t="n">
+        <v>714</v>
+      </c>
+      <c r="K75" t="n">
+        <v>547</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5099999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1444759206798867</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.569354838709677</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2722891566265061</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5736714975845411</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
